--- a/shopify-leads/Shopify_Inventory_Order_Automation_700_Leads.xlsx
+++ b/shopify-leads/Shopify_Inventory_Order_Automation_700_Leads.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duplicates_Removed" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shopify_Leads'!$A$1:$AE$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs_Review'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shopify_Leads'!$A$1:$AE$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs_Review'!$A$1:$AE$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Duplicates_Removed'!$A$1:$AE$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -624,8 +624,1764 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2 Hounds Design</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://2houndsdesign.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No-pull dog harnesses, collars and leashes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Alisha Navarro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Alisha</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Founder/Owner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>woof@2houndsdesign.com</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://2houndsdesign.com/products/black-freedom-no-pull-dog-harness</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Freedom No-Pull Harness in 5/8" (XS–M) and 1" (M–XXL) widths, plus harness bundles</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>The Freedom No-Pull Harness is offered in two strap widths with overlapping Medium sizes, across many colours, plus 'BUNDLE!' listings like the 1980s and Sharky Party sets.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Variant-level low-stock alerts by width/size/colour that also update the related bundle listings and notify production.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Width x size x colour creates many variants, and bundles pull from the same harness stock; founder interview mentions own factory, so production notifications fit.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Freedom Harness size alerts</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Hi Alisha,
+I noticed the Freedom No-Pull Harness comes in both 5/8" and 1" widths, each with its own size range, in many colours, and several prints are also sold as bundles like the Sharky Party set. That adds up to a lot of variants to watch as holiday orders pick up.
+I help Shopify stores automate inventory updates, order routing and supplier or production notifications. For example, when a specific width and size drops below a set level, your production team could receive an automatic alert and the matching bundle could update at the same time.
+Which variants are usually the first to run low for you?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://2houndsdesign.com/products/reflective-black-freedom-no-pull-dog-harness</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://2houndsdesign.com/pages/donatedecember</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>US-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Branch Basics</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://branchbasics.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Non-toxic concentrate cleaning and laundry products with refillable bottles</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Allison Evans</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Allison</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>info@branchbasics.com</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://branchbasics.com/collections/starter-kits?page=2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Starter kits (choose refillable plastic or glass bottles); Ultimate Starter Kit with 33.8 oz Concentrate, Laundry Detergent, Oxygen Boost, Dishwasher Tablets and 4 refillable bottles</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Branch Basics starter kits let customers choose refillable plastic or glass bottles, and the Ultimate Starter Kit combines the Concentrate, Laundry Detergent, Oxygen Boost, Dishwasher Tablets and four bottles.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Kit-component inventory sync (bottle type plus each included product) and concentrate refill reminders triggered from starter-kit orders.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Each kit pulls from several individual SKUs and a plastic/glass bottle option, and the concentrate model drives repeat refill orders.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Starter kit components at Branch Basics</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Hi Allison,
+I noticed your starter kits let customers pick refillable plastic or glass bottles, and the Ultimate Starter Kit pulls together the Concentrate, Laundry Detergent, Oxygen Boost, Dishwasher Tablets and four bottles.
+Since each kit depends on several separate items, a shortage of glass bottles or one product can affect the whole kit. I build Shopify automation systems for inventory updates, order processing and supplier notifications. One idea is to tie kit availability to component stock, then follow each kit order with a concentrate refill reminder timed to typical usage.
+Which part of the kit is usually hardest to keep in stock?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://branchbasics.com/products/ultimate-starter-kit</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>https://branchbasics.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>US-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Field Company</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://fieldcompany.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lightweight smooth cast iron cookware</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stephen Muscarella</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>help@fieldcompany.com</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://fieldcompany.com/collections/cast-iron-gifts</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Skillet sets: 3-Piece Set (No.4, No.8, No.12), 5-Piece Set, 9-Piece Set (five skillets, four lids), Starter Set No.8</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Field Company sells skillets individually and in 3-, 5- and 9-piece sets, with headquarters in New York City and production and fulfillment facilities in Indiana, Illinois and Wisconsin.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Bundle-aware inventory sync so set availability is calculated from component skillet and lid stock across the multiple fulfillment facilities.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sets share the same component skillets and lids, and stock sits across several facilities; automating component-based set availability keeps listings accurate.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Keeping Field's skillet sets in sync</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Hi Stephen,
+I noticed Field sells its skillets both on their own and in 3-, 5- and 9-piece sets, and that fulfillment runs through facilities in Indiana, Illinois and Wisconsin.
+When the same No.8 or No.12 sits inside several sets, one busy week can shift what's really available. I build Shopify automations that make inventory updates, order routing and supplier notifications easier to manage. A practical example: set availability calculated automatically from component skillet and lid counts at each facility, so a set pauses only when a part runs out.
+Are your sets tracked as their own stock today, or built from components?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://fieldcompany.com/products/nine-piece-cast-iron-cookware-set</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>https://fieldcompany.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>US-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Giant Dog Gear</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://giantdoggear.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Heavy-duty collars and rope leashes for large dogs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>info@giantdoggear.com</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/025mdwpgzv</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Martingale Collar with Cobra Buckle, Heavy Duty Dog Collar, Field Training Leash, 'Tiny Giant' small-dog line</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Gear is handmade in Bend, Oregon with MIL-SPEC Cobra buckles and climbing rope, and the range now spans giant-breed collars plus a 'Tiny Giant' line for small dogs.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Component-level inventory (Cobra buckles, webbing, rope, clips) that decrements per order and triggers supplier reorder alerts.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Handmade products depend on hardware components; tracking components prevents listing items that can't be built.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Cobra buckle stock alerts</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Hi Giant Dog Gear team,
+I liked seeing that your collars and rope leashes are handmade in Bend, Oregon with MIL-SPEC Cobra buckles and woven-core climbing rope, and that the Tiny Giant line now covers small dogs too. For handmade gear, the parts on the shelf matter as much as finished stock.
+I create Shopify automations that simplify inventory updates, order processing and supplier notifications. One example: each order deducts the buckles, webbing and rope it uses, and you get an automatic reorder alert before a component runs short ahead of the holidays.
+Do you currently track hardware separately from finished products?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://giantdoggear.com/products/martingale-collar-with-cobra-buckle-giant-dog-collar</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>https://giantdoggear.com/policies/contact-information</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>US-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gracie's Doggie Delights</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://graciesdoggiedelights.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Single-ingredient freeze-dried dog and cat treats</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grace Jagler</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gracie@graciesdoggiedelights.com</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Decision-maker</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/graciesdoggiedelights/collections/286609146014/gracies-pet-treats</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Gracie's Pet Treats and Gracie's Kitty Delights (freeze-dried chicken breast, hearts, salmon, minnows), training treats 4oz bags, bulk bags</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Alongside the dog treat line, there is a separate Kitty Delights cat line, plus 4oz training treat bags and bulk bags of the same freeze-dried proteins.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Link bag sizes (4oz vs bulk) to shared protein batch inventory so stock across dog, cat and bulk listings updates from one count.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Same freeze-dried proteins appear in multiple pack sizes and lines; batch-level tracking keeps listings accurate.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Freeze-dried batch tracking for Gracie's</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Hi Grace,
+I enjoyed browsing Gracie's Doggie Delights and saw that the freeze-dried proteins come in regular bags, 4oz training treats and bulk bags, plus the Kitty Delights line for cats. With holiday gifting coming up, keeping every bag size accurate from the same batch of chicken or salmon can take time.
+I build Shopify automation systems that make inventory updates, order processing and supplier notifications simpler. One workflow: you enter each finished batch once, and the stock for all related bag sizes adjusts automatically as orders come in.
+Would tracking by batch like that be helpful for you?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://graciesdoggiedelights.com/collections/all</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>https://graciesdoggiedelights.com/policies/contact-information</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>US-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Leeds Dog Supply</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://leedsdogsupply.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>California-made dog collars, leashes and accessories</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sales@leedsdogsupply.com</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/1z9cyu3bw8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Named matching collections (Hank, Lynx, Dazey, Rover, Poncho) with collar and leash; Hank Collar from $19.95, Hank Leash $25.95</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Collars and leashes are grouped into named collections such as Hank, Lynx, Dazey, Rover and Poncho, and the brand also sells through stockists.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Shared inventory between DTC and stockist/wholesale orders with low-stock alerts per collection pattern.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Matching collar/leash sets per pattern plus a stockist channel means the same webbing patterns serve two order streams.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Quick idea for the Hank Collection</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Hi Leeds Dog Supply team,
+I was browsing your named collections like Hank, Lynx and Dazey, where each pattern has a matching collar and leash made in California, and saw that you also supply stockists. When online and wholesale orders share the same patterns, it helps to see stock in one place, especially before the holidays.
+I build Shopify automation systems that simplify inventory updates, order processing and supplier notifications. One idea: stockist orders get tagged automatically, deduct from the same pattern inventory, and trigger an alert when a collection's webbing is close to running out.
+Would that kind of combined view be useful?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://leedsdogsupply.com/collections/hank-collection</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>https://leedsdogsupply.com/pages/stockists</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>US-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Material Kitchen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://materialkitchen.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Modern kitchen tools, knives and cutting boards</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Eunice Byun</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eunice</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hello@materialkitchen.com</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://materialkitchen.com/collections/sets</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>The rePrep Set (reBoard, grippy reBoard, mini reBoard) with colour options Cool Neutral, Almost Black, Mocha, Sage (Limited Edition)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>The rePrep Set bundles three reBoards, and add-ons come in colours including Cool Neutral, Almost Black, Mocha and a limited-edition Sage.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Colour-level stock alerts with a limited-edition sell-through tracker, and automatic hiding or back-in-stock signup when a colour in a set runs out.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sets combine several boards across colourways, including a limited-edition colour, so availability depends on multiple colour SKUs at once.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Sage limited edition stock idea</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Hi Eunice,
+I came across the rePrep Set on Material's site, with three reBoards and colour options like Cool Neutral, Almost Black, Mocha and the limited-edition Sage.
+A limited colour inside a multi-piece set is the kind of thing that can sell through faster than expected around the holidays. I help Shopify stores automate inventory updates, order processing and supplier notifications. One workflow I'd suggest: a colour-level tracker that alerts your team when Sage reaches a set threshold and switches the option to a waitlist automatically instead of leaving it to a manual check.
+How do you usually plan restocks for limited colours?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://materialkitchen.com/products/the-reprep-set</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>https://materialkitchen.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meliora Cleaning Products</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://meliorameansbetter.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Plastic-free household cleaning and laundry products with refills</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kate Jakubas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kate</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>info@meliorameansbetter.com</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://meliorameansbetter.com/policies/shipping-policy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Refills collection: Laundry Powder Detergent Refill (128 HE / 64 standard loads) in multiple scents, plus Laundry Refill Bundle</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Meliora's paper box laundry powder refills are designed to refill the paper-and-steel Laundry Powder canisters and come in several scents such as unscented, lavender and lemon.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Automated refill reminders/reorder flow triggered by canister or refill purchase date, plus scent-level stock alerts for the refill SKUs.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Refills are a repeat purchase tied to an earlier canister order and split across scent variants; timing reminders and watching scent stock keeps the refill cycle smooth.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Refill timing idea for Meliora</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Hi Kate,
+I was looking at Meliora's refills collection and liked how the paper box laundry powder refills are made to top up the paper-and-steel canisters, with scents from unscented to lavender and lemon.
+Refills tend to follow a predictable cycle, which makes them a good fit for automation. I set up Shopify workflows that take the manual steps out of stock updates, order handling and supplier alerts. For example, a customer who bought a canister could get a refill reminder around when the box usually runs out, while you get a heads-up if one scent is running low.
+Do most refill customers reorder on their own today?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://meliorameansbetter.com/collections/refills</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>https://meliorameansbetter.com/policies/shipping-policy</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>US-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Piper Loop Pets</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://piperlooppets.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>USA-made dog training treats in refillable tins and pouches</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Co-founders (Carol and Anna, surnames not verified)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>info@piper-loop.com</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/piperlooppets</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026 Lil Biscuit Treat Pouches (freeze-dried meats or probiotic soft chews), refillable pocket training tins</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>The 2026 Lil Biscuit Treat Pouches collection lets customers choose freeze-dried meats or probiotic chews, alongside refillable pocket training tins.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Refill reminder / reorder flow tied to tin purchases plus stock alerts per pouch option.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Refillable tins imply repeat refill purchases; pouches come in two treat options to track separately.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Refill idea for Piper Loop tins</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Hi Piper Loop Pets team,
+I came across your refillable pocket training tins and the 2026 Lil Biscuit Treat Pouches, where customers pick freeze-dried meats or probiotic soft chews. Refillable products are a nice fit for repeat orders, especially heading into the holiday season.
+I set up Shopify automations that simplify inventory updates, order processing and supplier notifications. For you, one idea is a workflow that sends a refill reminder a few weeks after a tin order, while tracking stock for each pouch option and alerting you before a flavor gets low.
+Do most customers come back for refills on their own today?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>https://piperlooppets.com/collections/2026-lil-biscuit-treat-pouches</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>https://piperlooppets.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>US-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Preen Pets</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://preenpets.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Natural USA-made dog treats and dog food</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ron Albeg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>info@PreenPets.com</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/preenpets</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>40+ natural dog treat varieties (jerky, bully sticks, Turkey Tendon Twists) and Whole Ingredient Dog Food (from 4 lb bag)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Preen Pets makes over 40 varieties of natural dog treats in its Eldred, Pennsylvania kitchen and also sells a Whole Ingredient Dog Food starting at a 4 lb bag.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Production-linked stock alerts across 40+ treat SKUs plus wholesale order routing separate from retail.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Large in-house-made catalog and a wholesale program both draw from the same kitchen output.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>40+ treats, one stock view</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Hi Ron,
+I noticed Preen Pets produces more than 40 natural treat varieties in your Eldred kitchen, from chicken jerky to Turkey Tendon Twists, plus the Whole Ingredient Dog Food. With retail and wholesale orders both drawing on the same production, holiday weeks can get busy.
+I build Shopify automation systems that help stores simplify inventory updates, order handling and supplier notifications. One idea: a daily low-stock summary for the kitchen that lists which treat varieties need a new batch, with wholesale orders tagged and routed separately from retail.
+Would a daily batch list like that save your team time?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>https://www.preenpets.com/collections/all</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>https://www.preenpets.com/contact/</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>US-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sassy Woof</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://sassywoof.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dog harnesses, collars, leashes and bundles</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Christine Chang</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>hello@sassywoof.com</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.sassywoof.com/collections/dog-harnesses-adjustable</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Adjustable Harnesses (XXS–XXL, sized by neck/chest) and Harness Three Piece Bundles</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Adjustable harnesses run XXSmall to XXLarge with separate size charts per harness type, and many prints are also sold as three-piece bundles (e.g. Harry Potter bundle).</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Bundle-aware inventory sync: when one size of a harness sells out, automatically update the matching bundle variants and flag low-stock sizes before holiday demand.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundles share components with single harness/collar/leash SKUs across many sizes, so stock needs to stay consistent across both listings.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Harness bundle stock idea for Sassy Woof</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Hi Christine,
+I was looking at Sassy Woof's adjustable harnesses and noticed each print comes in sizes from XXSmall to XXLarge, with many also sold as three-piece bundles like the Harry Potter set. With the holiday season approaching, keeping single items and bundles in sync by size can get tricky.
+I build Shopify automations that simplify inventory updates, order processing and supplier notifications. One idea: when a harness size runs low, the bundle using that size updates automatically and your team gets a short restock alert listing the exact print and size.
+Would something like that be useful for your bundle lineup?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://www.sassywoof.com/collections/dog-bundles</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>https://www.sassywoof.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>US-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Stargazer Cast Iron</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://stargazercastiron.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Made-in-USA cast iron cookware</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Peter Huntley</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>info@stargazercastiron.com</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://stargazercastiron.com/policies/terms-of-service</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Cookware collection: 10.5-inch and 12-inch cast iron skillets (each offered seasoned or bare) and 13.5-inch braiser</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Stargazer designs and manufactures its skillets in Allentown, PA, and both the 10.5-inch and 12-inch skillets come in seasoned or bare finishes.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Per-variant (size x finish) low-stock alerts tied to production planning, with automatic notification when a seasoned or bare variant drops below a threshold.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Each skillet size has two finish variants made in-house, so stock is split across several SKUs that depend on production runs; threshold alerts help match production to holiday demand.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Seasoned vs bare stock alerts for Stargazer</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Hi Peter,
+I noticed Stargazer makes its skillets in Allentown and offers both the 10.5-inch and 12-inch in seasoned or bare finishes. That means every size is really two separate stock items, each tied to your own production runs.
+With holiday gifting coming up, keeping those variants balanced can matter. I build Shopify automation systems that help stores simplify inventory updates, order processing and supplier notifications. One idea: an alert that flags when a specific size and finish falls below a set level, and sends a short summary to whoever schedules seasoning or casting.
+How do you currently decide which finish to produce next?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://stargazercastiron.com/collections/cookware</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>https://stargazercastiron.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
+  <autoFilter ref="A1:AE13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -636,7 +2392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -829,8 +2585,411 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REV-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Smithey Ironware</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://smithey.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cast iron and carbon steel cookware</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>support@smithey.com</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://smithey.com/policies/terms-of-service</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>The Founder's 3-Piece Set (No. 8 Chef Skillet, No. 10, No. 12 Cast Iron Skillets); Set of 4 No. 6 Skillets</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Smithey offers The Founder's 3-Piece Set with the No. 8 Chef, No. 10 and No. 12 skillets, as well as a Set of 4 No. 6 Skillets.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Component-based availability for multi-skillet sets and corporate gifting order routing.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sets reuse individual skillet SKUs and a separate corporate gifting channel exists (gifting@smithey.com).</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Skillet set stock idea for Smithey</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Hi Smithey team,
+I saw The Founder's 3-Piece Set pairs the No. 8 Chef, No. 10 and No. 12 skillets, and there's also a Set of 4 No. 6 Skillets alongside your corporate gifting program.
+When individual skillets also live inside sets and bulk gift orders, holiday demand can pull the same stock in several directions. I build Shopify automations that simplify inventory updates, order processing and supplier notifications. One workflow: set availability calculated from single-skillet counts, with large gifting orders flagged so they don't quietly drain retail stock.
+Are gifting orders handled in the same Shopify inventory as retail?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://smithey.com/products/the-founders-3-piece-set</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://smithey.com/a/faq/</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>US location not stated in search snippets (only an 843 phone number); likely mid-size/well-known brand; no decision maker verified.</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REV-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marquette Castings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://marquettecastings.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cast iron cookware</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>support@marquettecastings.com</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.marquettecastings.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Quick inventory idea for Marquette Castings</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Hi Marquette Castings team,
+I came across Marquette Castings while looking at independent cast iron makers, and your contact page made it easy to find the right inbox. As an independent cast iron maker, you likely see demand shift between sizes during gifting season.
+I build Shopify automation systems that help stores simplify inventory updates, order processing and supplier notifications. Ahead of the holiday season, a low-stock alert per skillet size can help plan casting runs earlier.
+How do you track stock across sizes today?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>https://www.marquettecastings.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; No verified product/collection detail and no US location statement in results (810 phone number only); email draft is generic and must be personalised before use.</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REV-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WanderDog Designs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://wanderdogdesigns.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Handmade yacht rope dog leashes and collars</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>wanderdogdesigns@gmail.com</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/5r0y4zdh18</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Rope Slip Lead; 'Small but Mighty' custom dog leashes collection; lifetime guarantee on rope leashes/collars</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Every leash and collar is handmade from yacht rope with a lifetime guarantee, and the Small but Mighty collection offers custom leashes.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Custom-order workflow: capture rope colour/length choices into a production queue and send automatic status updates.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Custom handmade items need order details passed cleanly to production.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Custom leash order flow idea</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Hi WanderDog Designs team,
+I noticed every leash and collar you make is handmade from yacht rope and backed by a lifetime guarantee, and the Small but Mighty collection offers custom leashes. Custom orders like these usually carry several details that need to reach the workbench correctly, especially as holiday orders start arriving.
+I build Shopify automations that simplify inventory updates, order processing and supplier notifications. One idea is a workflow that turns each custom order into a clear production ticket with the chosen options and sends the customer an automatic update when it ships.
+How do custom orders reach production for you today?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://wanderdogdesigns.com/collections/small-but-mighty</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>https://wanderdogdesigns.com/policies/refund-policy</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>email domain not the business; US location not verified in search results; email is a Gmail address (listed on own policy pages).</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
+  <autoFilter ref="A1:AE4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/shopify-leads/Shopify_Inventory_Order_Automation_700_Leads.xlsx
+++ b/shopify-leads/Shopify_Inventory_Order_Automation_700_Leads.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duplicates_Removed" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shopify_Leads'!$A$1:$AE$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs_Review'!$A$1:$AE$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shopify_Leads'!$A$1:$AE$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs_Review'!$A$1:$AE$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Duplicates_Removed'!$A$1:$AE$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE86"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No-pull dog harnesses, collars and leashes</t>
+          <t>Pet products and accessories</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USA-made MOLLE panels and interior storage for Toyota 4Runner, Tacoma, Tundra and Sequoia</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bean-to-bar chocolate</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Handmade-to-order colonial and farmhouse lighting (chandeliers, sconces, lanterns) from a Vermont workshop</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baby feeding: suction bowls, plates, spoons</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vegan, plastic-free makeup (lip, cheek, multi-sticks, Balmies)</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Crossbody phone cases and accessories</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wooden toys, blocks and baby teethers</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Natural skincare, self-tanners and body care (made in USA)</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Handmade formalwear and accessories for baby boys (Phoenix, AZ)</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Women's young contemporary clothing boutique (Austin, Texas)</t>
+          <t>Fashion and clothing brands</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Supplements, herbal teas and gummies</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Non-toxic concentrate cleaning and laundry products with refillable bottles</t>
+          <t>Kitchen and household products</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brazilian bikinis designed in California</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Small batch specialty coffee roaster</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ford Bronco and Raptor performance and off-road parts, including in-house USA-made items</t>
+          <t>Automotive accessories</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Plant-based haircare and skincare</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Phone cases and device accessories</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>American-made Jeep and Bronco parts and accessories (grab bars, door handles, mounts)</t>
+          <t>Automotive accessories</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Handcrafted luxury throw pillow covers and USA-filled pillow inserts</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Baby essentials: bandana bibs, knit swaddles, car seat covers</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Faith-inspired, hand-poured soy/coconut candles from Colorado Springs</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vintage-inspired menswear basics and denim (Los Angeles)</t>
+          <t>Fashion and clothing brands</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Techwear apparel (Los Angeles)</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lightweight smooth cast iron cookware</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Organic baby clothing, play gyms and toys</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Book-inspired soy candles and gifts for readers</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bean-to-bar chocolate</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Organic loose leaf wellness teas, samplers, subscription box</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>In-house CNC-made Jeep and Ford Bronco light mounts and accessories</t>
+          <t>Automotive accessories</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heavy-duty collars and rope leashes for large dogs</t>
+          <t>Pet products and accessories</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Engagement rings, wedding bands and fine jewelry</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ultralight backpacks and hiking gear</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Single-ingredient freeze-dried dog and cat treats</t>
+          <t>Pet products and accessories</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Weightlifting accessories (belts, grips, straps)</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small batch hot sauce</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Handmade pillow covers, inserts and home textiles sewn in a North Carolina studio</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Handmade stacking rings and jewelry (gold fill, rose gold fill, sterling, solid 14K)</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Handmade dolls, woodland animals and doll clothes</t>
+          <t>Fashion and clothing brands</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Craft hot sauce shop (gift sets, small batch sauces)</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Handcrafted solid hardwood furniture (beds, tables, dressers), made to order in the Midwest</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Handmade candles, soaps and skincare from Texas</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Desk setup and laptop stands</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Camping hammocks and outdoor gear</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Small batch hot sauce</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kettlebells and strength equipment</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Solid 14k gold and sterling silver fine jewelry, engagement rings, personalized rings</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Harley-Davidson motorcycle parts, suspension and accessories (retail store + online)</t>
+          <t>Automotive accessories</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>California-made dog collars, leashes and accessories</t>
+          <t>Pet products and accessories</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>USA-made car detailing chemicals</t>
+          <t>Automotive accessories</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lezat</t>
+          <t>Lindsey Leigh Jewelry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://lezat.com</t>
+          <t>https://lindseyleighjewelry.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Organic cotton women's activewear, made in Los Angeles</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jaleh Factor</t>
+          <t>Lindsey</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Jaleh</t>
+          <t>Lindsey</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>hi@lezat.com</t>
+          <t>hello@lindseyleighjewelry.com</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7871,184 +7871,35 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://shop.app/m/lezat</t>
+          <t>https://lindseyleighjewelry.com/policies/terms-of-service</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Activewear collection; Nova Organic Cotton Sport Dress (XS-XL, Black/Ivory)</t>
+          <t>Personalized collection (Birthstones, Engraveable, Initials &amp; Names); Diamond Personalized Name Ring up to 8 letters, sizes 5-8; Diamond Signet Ring with engraved letter, sizes 2-6</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Lezat makes its organic cotton activewear in-house in Los Angeles; styles like the Nova Organic Cotton Sport Dress run across multiple sizes and colours.</t>
+          <t>The Diamond Personalized Name Ring lets customers choose up to 8 letters in 14K gold (sizes 5-8), and the Diamond Signet Ring adds an engraved letter in block or script font.</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Variant-level low-stock alerts that automatically create production requests for the in-house LA sewing team.</t>
+          <t>Capture name/letter, font and size as structured fields and auto-generate production work orders plus customer confirmation of the personalization details.</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>In-house production plus many size/colour variants means online stock and cutting schedules must stay aligned; automated variant thresholds tie sales to production.</t>
+          <t>Personalized name and engraved signet rings require custom text, font and size per order, which benefits from automatic order-to-production handoff.</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Made-in-LA restock idea for Lezat</t>
+          <t>Name ring details, captured automatically</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
-        <is>
-          <t>Hi Jaleh,
-I was looking at the Lezat activewear collection and noticed how many styles, like the Nova Organic Cotton Sport Dress, run across several sizes and colours while being sewn in-house in Los Angeles. With holiday orders coming, keeping in-house production and online stock in step can get busy.
-I build Shopify automation systems that help stores simplify inventory updates, order processing and supplier notifications. One idea for Lezat: when a size or colour variant drops below a set level, Shopify automatically creates a cut-and-sew request for your LA team with recent sales attached.
-Would a variant-level production alert like that be useful for your team?
-Best regards,
-Oseni Ibrahim
-Shopify Automation &amp; Integration Specialist</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>https://www.lezat.com/collections/activewear</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>https://www.lezat.com/pages/orders-shipping</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>PUBLICLY_LISTED</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>NOT_SENT</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>NO_REPLY</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AE52" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>US-052</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Lindsey Leigh Jewelry</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://lindseyleighjewelry.com</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Fine and personalized jewelry (name rings, signet rings, birthstones)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Lindsey</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Lindsey</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Founder</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>hello@lindseyleighjewelry.com</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>General inbox</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>https://lindseyleighjewelry.com/policies/terms-of-service</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Personalized collection (Birthstones, Engraveable, Initials &amp; Names); Diamond Personalized Name Ring up to 8 letters, sizes 5-8; Diamond Signet Ring with engraved letter, sizes 2-6</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>The Diamond Personalized Name Ring lets customers choose up to 8 letters in 14K gold (sizes 5-8), and the Diamond Signet Ring adds an engraved letter in block or script font.</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Capture name/letter, font and size as structured fields and auto-generate production work orders plus customer confirmation of the personalization details.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Personalized name and engraved signet rings require custom text, font and size per order, which benefits from automatic order-to-production handoff.</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Name ring details, captured automatically</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
         <is>
           <t>Hi Lindsey,
 I noticed your Diamond Personalized Name Ring lets customers choose up to eight letters in 14K gold, and the Diamond Signet Ring adds an engraved letter in block or script font. Those details matter a lot, especially as holiday gift orders build up.
@@ -8059,145 +7910,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://lindseyleighjewelry.com/products/diamond-custom-name-ring</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>https://lindseyleighjewelry.com/policies/terms-of-service</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr">
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr">
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE53" t="n">
+      <c r="AE52" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>US-053</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>US-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Lineage Coffee Roasting</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>https://lineageroasting.com</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Specialty coffee roaster (subscriptions)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Jan Jarrett</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Co-founder</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>hello@lineageroasting.com</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>https://www.lineageroasting.com/collections/subscriptions</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Coffee Subscriptions collection (customer selects delivery frequency)</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Lineage's Coffee Subscriptions collection lets customers pick how often they want a delivery, and the team handles the rest.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Generate a weekly roast forecast from active subscriptions by coffee and frequency, and send an automatic low-stock alert for green coffee or bags before the next renewal batch.</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Customer-chosen frequencies mean renewal volumes vary week to week; a forecast tied to Shopify subscription data gives the roaster an early, accurate view.</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Quick idea for Lineage subscriptions</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>Hi Jan,
 I came across the Lineage Coffee Subscriptions page and liked the simple promise: customers choose how often they want coffee, and you take care of the rest. Behind that simplicity, renewal volumes can swing week to week, especially as holiday gifting picks up.
@@ -8208,145 +8059,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://www.lineageroasting.com/collections/subscriptions</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>https://www.lineageroasting.com/collections/subscriptions</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr">
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE54" t="n">
+      <c r="AE53" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>US-054</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>US-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Lisa Says Gah</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>https://lisasaysgah.com</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Women's fashion: in-house collection plus curated female-founded brands (San Francisco)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Lisa Bühler</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Lisa</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>teamgah@lisasaysgah.com</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>https://lisasaysgah.com/collections/lisa-says-gah-collection</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Lisa Says Gah Collection (in-house), e.g. Cory Turtleneck - Swans; physical stores in San Francisco (522 Octavia St, Hayes Valley) and Los Angeles</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Lisa Says Gah runs its own Lisa Says Gah Collection (e.g. the Cory Turtleneck in Swans) next to curated brands, and sells through a San Francisco store on Octavia Street and an LA store as well as online.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Multi-location stock sync and automatic transfer suggestions between the SF store, LA store and online warehouse for the in-house collection.</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Two physical stores plus online sharing the same in-house styles means size-level stock can sit in the wrong place; location-aware alerts and transfer suggestions help balance it.</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>SF, LA and online stock balance</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>Hi Lisa,
 I was browsing the Lisa Says Gah Collection, including the Cory Turtleneck in Swans, and noticed you sell through the Hayes Valley store on Octavia Street, the LA store and online.
@@ -8358,145 +8209,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://lisasaysgah.com/products/cory-sweater-swans</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>https://lisasaysgah.com/pages/contact</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr">
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr">
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE55" t="n">
+      <c r="AE54" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>US-055</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>US-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Lorier</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>https://lorierwatches.com</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Vintage-inspired mechanical watches and straps</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Jewelry and accessories</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Lorenzo Ortega and Lauren Ortega</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Lorenzo</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Co-founders</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>info@lorierwatches.com</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>https://www.lorierwatches.com/collections/accessories</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Accessories collection: Espresso Leather Strap in 18mm/20mm widths and several wrist sizes; Bonetto Cinturini 295 rubber strap (shown out of stock)</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Lorier sells straps alongside its watches, e.g. the Espresso Leather Strap in 18mm and 20mm widths with several wrist sizes, and some strap listings show as out of stock.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Low-stock and back-in-stock alerts per strap width/length variant, with automatic reorder notifications to strap suppliers.</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Strap variants (width x wrist size) and an out-of-stock third-party strap suggest variant-level stock tracking and supplier reorders are relevant.</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Strap variant stock at Lorier</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>Hi Lorenzo and Lauren,
 I was looking at Lorier's accessories and noticed straps like the Espresso Leather Strap come in 18mm and 20mm widths with several wrist sizes, while the Bonetto rubber strap was showing out of stock. Small accessories like these often sell alongside watches during the holidays.
@@ -8507,133 +8358,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://www.lorierwatches.com/products/espresso-leather-strap</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>https://www.lorierwatches.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr">
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE56" t="n">
+      <c r="AE55" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>US-056</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>US-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>MagBak</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>https://magbak.com</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Magnetic phone cases, chargers and mounts</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Electronics and accessories</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>info@magbak.com</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>https://shop.app/m/magbak</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>MagBak for iPhone 17 Series (Gen 2) + MagStick, sold for iPhone 17, 17 Air, 17 Pro and 17 Pro Max; MagBak Elite line</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>MagBak sells its Gen 2 case for iPhone 17, 17 Air, 17 Pro and 17 Pro Max, bundled with MagStick, alongside a MagBak Elite line for the same phones.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Bundle-aware inventory sync so that MagStick component stock is deducted with every case bundle sold and low-component alerts reach the supplier before bundles go out of stock.</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>A case + MagStick bundle across four phone models and two lines means a shared component's stock determines availability of many listings.</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>MagStick bundle stock for MagBak</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>Hi MagBak team,
 I saw that the Gen 2 iPhone 17 case ships with a MagStick and comes in versions for the 17, 17 Air, 17 Pro and 17 Pro Max, with the Elite line covering the same phones. When one component is shared across that many listings, its stock level quietly decides what can actually ship.
@@ -8644,145 +8495,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://magbak.com/products/magbak-for-iphone-17-series</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>https://magbak.com/pages/contact</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr">
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE57" t="n">
+      <c r="AE56" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>US-057</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>US-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Material Kitchen</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>https://materialkitchen.com</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Modern kitchen tools, knives and cutting boards</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Kitchen and household products</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Eunice Byun</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Eunice</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>hello@materialkitchen.com</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>https://materialkitchen.com/collections/sets</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>The rePrep Set (reBoard, grippy reBoard, mini reBoard) with colour options Cool Neutral, Almost Black, Mocha, Sage (Limited Edition)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>The rePrep Set bundles three reBoards, and add-ons come in colours including Cool Neutral, Almost Black, Mocha and a limited-edition Sage.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Colour-level stock alerts with a limited-edition sell-through tracker, and automatic hiding or back-in-stock signup when a colour in a set runs out.</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Sets combine several boards across colourways, including a limited-edition colour, so availability depends on multiple colour SKUs at once.</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Sage limited edition stock idea</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>Hi Eunice,
 I came across the rePrep Set on Material's site, with three reBoards and colour options like Cool Neutral, Almost Black, Mocha and the limited-edition Sage.
@@ -8793,145 +8644,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://materialkitchen.com/products/the-reprep-set</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>https://materialkitchen.com/pages/contact</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr">
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE58" t="n">
+      <c r="AE57" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>US-058</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>US-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Meliora Cleaning Products</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>https://meliorameansbetter.com</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Plastic-free household cleaning and laundry products with refills</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kitchen and household products</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Kate Jakubas</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Kate</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>info@meliorameansbetter.com</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>https://meliorameansbetter.com/policies/shipping-policy</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Refills collection: Laundry Powder Detergent Refill (128 HE / 64 standard loads) in multiple scents, plus Laundry Refill Bundle</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Meliora's paper box laundry powder refills are designed to refill the paper-and-steel Laundry Powder canisters and come in several scents such as unscented, lavender and lemon.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Automated refill reminders/reorder flow triggered by canister or refill purchase date, plus scent-level stock alerts for the refill SKUs.</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Refills are a repeat purchase tied to an earlier canister order and split across scent variants; timing reminders and watching scent stock keeps the refill cycle smooth.</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Refill timing idea for Meliora</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>Hi Kate,
 I was looking at Meliora's refills collection and liked how the paper box laundry powder refills are made to top up the paper-and-steel canisters, with scents from unscented to lavender and lemon.
@@ -8942,145 +8793,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://meliorameansbetter.com/collections/refills</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>https://meliorameansbetter.com/policies/shipping-policy</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr">
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE59" t="n">
+      <c r="AE58" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>US-059</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>US-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Meow Meow Tweet</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://meowmeowtweet.com</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Vegan skincare and body care with refill program</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Skincare and beauty products</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Tara Pelletier and Jeff Kurosaki</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Tara</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Co-founders</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>hello@meowmeowtweet.com</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>https://meowmeowtweet.com/pages/our-founders</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Refill Program</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Meow Meow Tweet runs a refill program; founded in Brooklyn in 2009 by Tara Pelletier and Jeff Kurosaki, the brand moved to Northern California in 2021 and products are handmade in Sacramento.</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Track refill pouches/bulk sizes separately from full packaging and auto-notify the team when refill stock or packaging materials fall below thresholds; tag refill orders automatically for packing.</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>A refill program adds a second packaging format per product; separate thresholds and order tags keep handmade batches and refill packaging planned together.</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Refill program stock alerts</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>Hi Tara,
 I read about the Meow Meow Tweet refill program and how everything is now made by hand in Sacramento. Offering refills next to standard packaging means each product really has two stock levels to watch, and that gets trickier when holiday orders pick up.
@@ -9091,133 +8942,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://meowmeowtweet.com/blogs/blog/our-refill-program</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>https://meowmeowtweet.com/pages/faq</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr">
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE60" t="n">
+      <c r="AE59" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>US-060</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>US-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>MONTA</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://montawatch.com</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Swiss-made automatic watches and straps</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Jewelry and accessories</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>info@montawatch.com</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>https://montawatch.com/products/monta-curved-end-leather-strap</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>MONTA Curved End Leather Strap in Black, Chocolate and Chestnut, fitting Oceanking V2, Skyquest, Atlas, Triumph and Noble</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>MONTA's Curved End Leather Strap comes in Black, Chocolate and Chestnut and fits five models (Oceanking V2, Skyquest, Atlas, Triumph, Noble); the brand is headquartered in St. Louis and also sells via authorized dealers.</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Map strap variants to compatible watch models so stock alerts and cross-sell/reorder notifications are triggered per model fit, and share stock levels with authorized dealers.</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>One strap SKU family spans colours and model fits, and the brand works with authorized dealers, so inventory visibility across channels is relevant.</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Curved-end strap stock across models</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>Hi MONTA team,
 I noticed your Curved End Leather Strap comes in Black, Chocolate and Chestnut and fits the Oceanking V2, Skyquest, Atlas, Triumph and Noble. With fits across five models and authorized dealers also selling MONTA, keeping strap stock clear before the holidays can take some coordination.
@@ -9228,133 +9079,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://montawatch.com/products/monta-curved-end-leather-strap</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>https://montawatch.com/pages/contact-monta</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr">
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr">
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE61" t="n">
+      <c r="AE60" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>US-061</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>US-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Moto Pockets</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://motopockets.com</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>USA-made motorcycle bags (windshield, handlebar, adventure/pannier bags)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Automotive accessories</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>sales@motopockets.com</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>https://shop.app/m/cdr7mhe1b0/collections/436381188348/motorcycle-windshield-bags</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Harley Windshield Bag (Classic) for Road King FLHR and Heritage Softail Classic FLSTC; Motorcycle Universal Windshield Bag (7"); 11" windshield bag; Harley T-Bar Handlebar Bag; Side Case Lid Bag</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Moto Pockets has made USA-made motorcycle bags since 2012, with model-specific items like the Classic Harley Windshield Bag for Road King FLHR and Heritage Softail Classic FLSTC in 1000D CORDURA, plus universal 7" and 11" windshield bags.</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Per-model stock alerts tied to sewing batches, and automatic routing of warranty-exchange requests (info@) separate from sales orders.</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Bags are made in the USA in model-specific and size-specific versions; a lifetime warranty program creates exchange orders alongside regular sales.</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Windshield bag stock alerts</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>Hi Moto Pockets team,
 I noticed your Classic Harley Windshield Bag is cut for the Road King FLHR and Heritage Softail Classic, next to universal 7-inch and 11-inch versions, all made in the USA. With model-specific bags and a lifetime warranty program, sales and exchanges can stack up before the holidays.
@@ -9365,145 +9216,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://www.motopockets.com/products/harley-davidson-motorcycle-windshield-bag-classic</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>https://www.motopockets.com/pages/contact</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr">
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr">
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE62" t="n">
+      <c r="AE61" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>US-062</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>US-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>No Maintenance</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://nomaintenance.us</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Men's and women's denim and outerwear (Los Angeles)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Roe Hodgson</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Roe</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>support@nomaintenance.us</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>https://shop.app/m/nomaintenance</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Denim collection, e.g. Haze Straight Leg Denim in Raw Indigo (waist 26-38) and Baggy Japanese Denim; shopping appointments page</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>No Maintenance's denim, like the Haze Straight Leg Denim in Raw Indigo, runs in waist sizes 26 to 38, several styles use Japanese denim, and the site also books in-person shopping appointments.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Waist-size low-stock alerts on denim and automatic stock holds/notes for items reserved for upcoming shopping appointments.</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Seven waist sizes per wash across multiple fits plus in-person appointments means online and appointment demand draw on the same stock; automation keeps them aligned.</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Haze denim waist-size alerts</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>Hi Roe,
 I came across No Maintenance and the Haze Straight Leg Denim in Raw Indigo, offered in waist sizes 26 through 38. I also saw that customers can book shopping appointments, so the same stock serves both online orders and in-person visits.
@@ -9515,133 +9366,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://nomaintenance.us/collections/denim</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>https://nomaintenance.us/policies/refund-policy</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr">
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE63" t="n">
+      <c r="AE62" t="n">
         <v>84</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>US-063</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>US-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Noble</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://shopnoble.com</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Sustainable women's and kids' clothing made in San Diego</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Baby and children's products</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>support@shopnoble.com</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>https://shop.app/m/shopnoble/collections/shop_all</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Adult Dresses collection (sizes XXS-3X, many prints/solids) and Noble Kids (0-3 months to 7 years, colours like navy, plaid, oat milk)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Noble makes its clothes in San Diego and ships from a San Diego warehouse; the Adult Dresses collection runs XXS to 3X while Noble Kids runs from 0-3 months to 7 years.</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Low-stock alerts across the two size ranges with an automatic production/reorder note to the San Diego production team when a print drops below a threshold.</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Two wide size ranges (adult XXS-3X and kids 0-3m-7y) across multiple prints create many variants; local production makes threshold-based reorder notifications practical.</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Quick stock idea for Noble</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>Hi Noble team,
 I enjoyed reading that your clothing is made in San Diego and ships from your warehouse there. Between the Adult Dresses collection in XXS to 3X and Noble Kids from newborn sizes up to age 7, that is a lot of size and print combinations to keep track of.
@@ -9653,133 +9504,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://shopnoble.com/collections/adult-dresses</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>https://shopnoble.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr">
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr">
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE64" t="n">
+      <c r="AE63" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>US-064</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>US-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Of Her Own Kind</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://ofherownkind.com</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Womenswear dresses made in New York (organic/linen)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>studio@ofherownkind.com</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>https://shop.app/m/ofherownkind</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Mirabelle Dress (The Mirabelle collection) in many colourways, e.g. Organic Sage Plaid, Tea Floral, Bluebell Linen, Black Linen; sizes XS-XXL; separate Ready-to-Ship collection</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>The Mirabelle Dress comes in a long list of colourways (Organic Sage Plaid, Tea Floral, Bluebell Linen, Black Linen and more) in XS-XXL, and the site also has a dedicated Ready-to-Ship collection.</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Automatically add/remove Mirabelle variants from the Ready-to-Ship collection based on live size stock, with low-stock alerts per colourway and size.</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Many colourway x size combinations plus a stock-dependent Ready-to-Ship collection means collection membership and stock levels must stay in sync; rule-based automation keeps them aligned.</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Mirabelle colourways and Ready-to-Ship</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>Hi Of Her Own Kind team,
 I was looking at the Mirabelle Dress and noticed how many colourways it now comes in, from Organic Sage Plaid and Tea Floral to Bluebell and Black Linen, each in XS to XXL. You also keep a separate Ready-to-Ship collection.
@@ -9791,145 +9642,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://ofherownkind.com/collections/the-mirabelle/products/mirabelle-dress-in-organic-sage-plaid</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>https://ofherownkind.com/pages/contact</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr">
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr">
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE65" t="n">
+      <c r="AE64" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>US-065</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>US-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Ornot</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://ornotbike.com</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Cycling apparel</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>info@ornotbike.com</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>https://www.ornotbike.com/products/mens-merino-riding-shirt-emerald</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Men's Merino Wool Cycling Shirt - Emerald; Men's UV Trail Shirt - Sage 415; Men's Mission Pants - Coffee (colourways listed as separate products)</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Ornot lists each colourway as its own product page, such as the Men's Merino Wool Cycling Shirt in Emerald and the Men's UV Trail Shirt in Sage 415, and has a San Francisco retail presence.</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Sync inventory between online store and retail location, and send size-level low-stock alerts across colourway product pages.</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Colourways are split into separate products (each with sizes), and the brand hires retail team members, so cross-channel and per-size stock syncing is a relevant workflow.</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Colourway stock sync for Ornot</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>Hi Matt,
 I noticed Ornot gives each colourway its own page, like the Merino Wool Cycling Shirt in Emerald and the UV Trail Shirt in Sage 415, and that you also run a retail space in San Francisco. Keeping sizes balanced across separate colour pages and the shop floor can take attention, especially before the holidays.
@@ -9940,133 +9791,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://www.ornotbike.com/products/mens-merino-riding-shirt-emerald</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>https://returns.ornotbike.com/</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr">
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr">
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE66" t="n">
+      <c r="AE65" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>US-066</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>US-065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Oveja Negra Bikepacking</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>https://ovejanegrabikepacking.com</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Bikepacking bags</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>info@ovejanegrathreadworks.com</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>https://www.ovejanegrabikepacking.com/collections/all</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Bodega Full Frame Bike Bag (4 sizes Small-XL, ~5-8L); 1/2 Pack 2.0 Partial Frame Bag (4 sizes, 5 colours; standard colourway marked sold out); Wack Pack colour combos</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Oveja Negra sews the Bodega full frame bag in four sizes from Small to XL in Salida, CO, and the 1/2 Pack 2.0 comes in four sizes and five colours, with the standard colourway showing sold out while Wack Pack versions are listed.</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Back-in-stock alerts per size/colour combination tied to the sewing production schedule, so restocks of a sold-out size automatically notify waiting customers.</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Handmade bags in many size/colour combinations, with at least one colourway sold out, suggest variant-level waitlists linked to production batches.</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>1/2 Pack restock alerts</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>Hi Oveja Negra team,
 I noticed the 1/2 Pack 2.0 comes in four sizes and five colours, and that the standard colourway was showing sold out while the Wack Pack versions were still available. Since everything is sewn in Salida, restocks probably follow your production batches.
@@ -10077,145 +9928,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>https://www.ovejanegrabikepacking.com/products/1-2-pack-2-0-frame-bag</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>https://www.ovejanegrabikepacking.com/pages/contact</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr">
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE67" t="n">
+      <c r="AE66" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>US-067</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>US-066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Petite Studio</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>https://petitestudionyc.com</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Petite womenswear (New York)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pet products and accessories</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Jenny Wang-Howell</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Jenny</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Founder &amp; CEO</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>support@petitestudionyc.com</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>https://shop.app/m/petitestudionyc/collections/shop_all</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Petite Jeans collection, Petite Basics, Spring/Summer '26 collections; sizes XXS-XXL with ~10 colour filters (wool coats, merino sweaters, mohair cardigans)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Petite Studio runs seasonal drops (Spring '26, Summer '26) next to evergreen collections like Petite Basics and Petite Jeans, with sizes from XXS to XXL.</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Automatically roll low-stock seasonal items into or out of collections and alert the team when core Petite Basics/Petite Jeans sizes drop below a threshold.</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Seasonal collections plus always-on basics across XXS-XXL create many variants with different replenishment needs; threshold alerts and auto-collection rules reduce manual merchandising.</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Petite Basics restock alerts</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>Hi Jenny,
 I noticed Petite Studio keeps evergreen collections like Petite Basics and Petite Jeans running next to seasonal drops such as Spring '26 and Summer '26, all sized from XXS to XXL.
@@ -10227,145 +10078,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://www.petitestudionyc.com/collections/petite-basics</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>https://www.petitestudionyc.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr">
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr">
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE68" t="n">
+      <c r="AE67" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>US-068</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>US-067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>Piper Lane Kids Co</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>https://piperlanekidsco.com</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Handmade infant &amp; toddler moccasins and accessories (Texas)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Baby and children's products</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Bree</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Bree</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Owner &amp; Founder</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>hello@piperlanekidsco.com</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>https://shop.app/m/xqj12zkd5m</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>PLKC moccasins (Hexies, Summer Dots, Pink Cactus, Chambray Moths) in sizes 0-8</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Piper Lane Kids Co hand-constructs its moccasins in Texas, with many prints offered in sizes 0 through 8.</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Deduct raw materials (cotton fabric, suede soles) per order and send automatic material reorder notes.</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Handmade, print-driven moccasins depend on fabric and sole availability; tracking materials alongside finished-goods variants supports holiday gifting demand.</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Moccasin materials tracking for Piper Lane</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>Hi Bree,
 I came across Piper Lane Kids Co and loved the moccasin prints like Hexies, Summer Dots and Pink Cactus, each offered in sizes 0 to 8 and hand-constructed in Texas. With holiday gifting season approaching, handmade stock across that many print and size combinations can be tricky to keep track of.
@@ -10376,137 +10227,137 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://www.piperlanekidsco.com/products/plkc-hexies-moccasin</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>https://www.piperlanekidsco.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr">
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr">
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE69" t="n">
+      <c r="AE68" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>US-069</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>US-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Piper Loop Pets</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://piperlooppets.com</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>USA-made dog training treats in refillable tins and pouches</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pet products and accessories</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Co-founders (Carol and Anna, surnames not verified)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>info@piper-loop.com</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>https://shop.app/m/piperlooppets</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>2026 Lil Biscuit Treat Pouches (freeze-dried meats or probiotic soft chews), refillable pocket training tins</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>The 2026 Lil Biscuit Treat Pouches collection lets customers choose freeze-dried meats or probiotic chews, alongside refillable pocket training tins.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>Refill reminder / reorder flow tied to tin purchases plus stock alerts per pouch option.</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Refillable tins imply repeat refill purchases; pouches come in two treat options to track separately.</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Refill idea for Piper Loop tins</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>Hi Piper Loop Pets team,
 I came across your refillable pocket training tins and the 2026 Lil Biscuit Treat Pouches, where customers pick freeze-dried meats or probiotic soft chews. Refillable products are a nice fit for repeat orders, especially heading into the holiday season.
@@ -10517,145 +10368,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://piperlooppets.com/collections/2026-lil-biscuit-treat-pouches</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>https://piperlooppets.com/pages/contact</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr">
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr">
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE70" t="n">
+      <c r="AE69" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>US-070</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>US-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Preen Pets</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>https://preenpets.com</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Natural USA-made dog treats and dog food</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Pet products and accessories</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Ron Albeg</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Ron</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>info@PreenPets.com</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>https://shop.app/m/preenpets</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>40+ natural dog treat varieties (jerky, bully sticks, Turkey Tendon Twists) and Whole Ingredient Dog Food (from 4 lb bag)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Preen Pets makes over 40 varieties of natural dog treats in its Eldred, Pennsylvania kitchen and also sells a Whole Ingredient Dog Food starting at a 4 lb bag.</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Production-linked stock alerts across 40+ treat SKUs plus wholesale order routing separate from retail.</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Large in-house-made catalog and a wholesale program both draw from the same kitchen output.</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>40+ treats, one stock view</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>Hi Ron,
 I noticed Preen Pets produces more than 40 natural treat varieties in your Eldred kitchen, from chicken jerky to Turkey Tendon Twists, plus the Whole Ingredient Dog Food. With retail and wholesale orders both drawing on the same production, holiday weeks can get busy.
@@ -10666,145 +10517,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>https://www.preenpets.com/collections/all</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>https://www.preenpets.com/contact/</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr">
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr">
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE71" t="n">
+      <c r="AE70" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>US-071</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>US-070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Press Coffee Roasters</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://presscoffee.com</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Specialty coffee roaster (beans, subscriptions)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Steve Kraus</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Steve</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Co-founder</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>info@presscoffee.com</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>https://presscoffee.com/collections/coffee-subscriptions</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Coffee subscriptions in 12 oz, 2 lb and 5 lb sizes with weekly, bi-weekly or monthly delivery and free bags on the 5th/10th/15th/20th shipment</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Press offers subscription coffees in 12 oz, 2 lb and 5 lb sizes, several grind options, and rewards a free bag on the 5th, 10th, 15th and 20th shipments.</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Automatically forecast green/roasted coffee needs from upcoming subscription renewals by size and grind, and tag milestone (5th/10th/15th/20th) orders so the free bag is added to the roast and pack list.</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Multiple sizes x grinds x frequencies plus milestone rewards create many roast/pack combinations each cycle; automated renewal forecasts and order tags keep roasting and packing aligned.</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Subscription roast planning for Press</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>Hi Steve,
 I was looking at the Press Coffee subscriptions and noticed you offer 12 oz, 2 lb and 5 lb sizes, several grind options, and a free bag on the 5th, 10th, 15th and 20th shipments. That is a generous program, and with the holidays approaching the mix of renewals and gift orders can shift quickly.
@@ -10815,145 +10666,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://presscoffee.com/collections/coffee-subscriptions</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>https://presscoffee.com/pages/refund-policy</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr">
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr">
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE72" t="n">
+      <c r="AE71" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>US-072</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>US-071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>Primally Pure</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>https://primallypure.com</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Natural skincare and body care</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Skincare and beauty products</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Bethany McDaniel</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Bethany</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>hello@primallypure.com</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>https://primallypure.com/collections/recently-launched-products</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>New Products + Bundles collection (Clean Teen Kit, The Tinted Duo, Mask and Mist trios)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Primally Pure's New Products + Bundles collection includes kits such as the Clean Teen Kit, The Tinted Duo and Mask and Mist trios. Founder Bethany McDaniel is based in Southern California.</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Component-level stock sync for kits and duos, with automatic low-stock alerts to the team/suppliers when a shared component limits kit availability.</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Kits draw from the same single-product inventory, so syncing components avoids kits staying live when a component runs low, especially around launches.</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>Quick kit inventory idea for Primally Pure</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>Hi Bethany,
 Your New Products + Bundles collection caught my eye, especially the Clean Teen Kit and The Tinted Duo. Kits like these pull from the same stock as the single products, so a launch or holiday rush can drain one shared item faster than expected.
@@ -10964,145 +10815,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>https://primallypure.com/collections/recently-launched-products</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>https://primallypure.com/pages/contact</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr">
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr">
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE73" t="n">
+      <c r="AE72" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>US-073</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>US-072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>PRx Performance</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>https://prxperformance.com</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Home gym equipment (folding squat racks, benches)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Brian Brasch</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Brian</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Co-founder</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>sales@prxperformance.com</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>https://prxperformance.com/collections/flexify/products/profile-folding-bench</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Profile CORE Low Ceiling squat rack; Desert Tan Profile PRO squat rack; Profile Flat Folding Weight Bench</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>PRx Performance offers its Profile squat racks in several configurations, including a Profile CORE Low Ceiling version and a Desert Tan Profile PRO, shipped from its warehouse in Fargo, ND, with a FAQ noting orders can take 2-4 weeks for the entire order to ship.</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Automated multi-item order status updates and split-shipment notifications, plus low-stock alerts per rack configuration and colour.</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>The FAQ states full orders can take 2-4 weeks to ship from Fargo, and racks come in multiple configurations/colours, so automated status and stock notifications per variant are a fitting improvement.</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Profile rack order updates</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>Hi Brian,
 I was reading about the Profile rack range, including the CORE Low Ceiling and the Desert Tan Profile PRO, and noticed your FAQ mentions that a full order can take 2-4 weeks to ship from Fargo. With the holiday season approaching, customers ordering a rack, bench and accessories together will want clear updates.
@@ -11113,133 +10964,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>https://prxperformance.com/products/profile-core-low-ceiling-squat-rack</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>https://prxperformance.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr">
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr">
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE74" t="n">
+      <c r="AE73" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>US-074</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>US-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>Ripclean</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>https://ripclean.com</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Car detailing soaps, kits and cleaning accessories</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Skincare and beauty products</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
         <is>
           <t>contact@ripclean.com</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>https://shop.app/m/ripclean</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Blizzard Extreme Foaming Car Soap (16 oz, 32 oz, gallon); Exterior Wash Kit with foam cannon (16/32 oz/gallon); Extreme Bucket Bundle; Complete Fabric Cleaning Kit</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Ripclean ships every order from Utah and sells its Blizzard Extreme Foaming Car Soap in 16 oz, 32 oz and gallon sizes, also inside kits like the Exterior Wash Kit with foam cannon and the Extreme Bucket Bundle.</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Kit-component inventory sync so kit sales deduct soap and foam cannon stock by size, plus a hold/edit window workflow for order changes before processing.</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Soap is sold standalone and inside kits in three sizes; their shipping policy asks customers to email quickly for order changes before processing.</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Blizzard soap kit inventory</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>Hi Ripclean team,
 I saw the Blizzard Extreme Foaming Car Soap comes in 16 oz, 32 oz and gallon sizes and also ships inside the Exterior Wash Kit with the foam cannon. With the same soap moving through single bottles and kits, the holiday season can make counts tricky.
@@ -11250,145 +11101,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>https://ripclean.com/products/blizzard-high-foaming-car-soap</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>https://ripclean.com/pages/contact</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr">
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr">
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE75" t="n">
+      <c r="AE74" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>US-075</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>US-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>Sassy Woof</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>https://sassywoof.com</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Dog harnesses, collars, leashes and bundles</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pet products and accessories</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Christine Chang</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Christine</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>hello@sassywoof.com</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>https://www.sassywoof.com/collections/dog-harnesses-adjustable</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Adjustable Harnesses (XXS–XXL, sized by neck/chest) and Harness Three Piece Bundles</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Adjustable harnesses run XXSmall to XXLarge with separate size charts per harness type, and many prints are also sold as three-piece bundles (e.g. Harry Potter bundle).</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Bundle-aware inventory sync: when one size of a harness sells out, automatically update the matching bundle variants and flag low-stock sizes before holiday demand.</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Bundles share components with single harness/collar/leash SKUs across many sizes, so stock needs to stay consistent across both listings.</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Harness bundle stock idea for Sassy Woof</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>Hi Christine,
 I was looking at Sassy Woof's adjustable harnesses and noticed each print comes in sizes from XXSmall to XXLarge, with many also sold as three-piece bundles like the Harry Potter set. With the holiday season approaching, keeping single items and bundles in sync by size can get tricky.
@@ -11399,133 +11250,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>https://www.sassywoof.com/collections/dog-bundles</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>https://www.sassywoof.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr">
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr">
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE76" t="n">
+      <c r="AE75" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>US-076</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>US-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Senita Athletics</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>https://senitaathletics.com</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Women's activewear (leggings, sports bras)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Support@senitaathletics.com</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>https://www.senitaathletics.com/collections/leggings</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Leggings in multiple inseams (23"-31"), sizes XXS-XXL; Meredith 7/8 Leggings</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Senita Athletics offers many leggings in several inseam lengths from 23 to 31 inches on top of sizes XXS-XXL.</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Low-stock alerts grouped by style, size and inseam with an auto-generated supplier reorder list.</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Inseam as a third option multiplies variants; grouped alerts make restocking decisions faster before the holiday rush.</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Inseam-level stock alerts for Senita</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>Hi Senita Athletics team,
 I noticed many of your leggings come in several inseam lengths, from 23 to 31 inches, on top of sizes XXS to XXL, including styles like the Meredith 7/8 Leggings. Adding inseam as a third option multiplies the variants to watch, and the holiday rush tends to show gaps quickly.
@@ -11536,145 +11387,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>https://www.senitaathletics.com/products/meredith-pocket-pants-23-in-inseam-black-white</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>https://www.senitaathletics.com/pages/contact</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr">
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr">
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE77" t="n">
+      <c r="AE76" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>US-077</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>US-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Stargazer Cast Iron</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>https://stargazercastiron.com</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Made-in-USA cast iron cookware</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kitchen and household products</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Peter Huntley</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>info@stargazercastiron.com</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>https://stargazercastiron.com/policies/terms-of-service</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Cookware collection: 10.5-inch and 12-inch cast iron skillets (each offered seasoned or bare) and 13.5-inch braiser</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Stargazer designs and manufactures its skillets in Allentown, PA, and both the 10.5-inch and 12-inch skillets come in seasoned or bare finishes.</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>Per-variant (size x finish) low-stock alerts tied to production planning, with automatic notification when a seasoned or bare variant drops below a threshold.</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>Each skillet size has two finish variants made in-house, so stock is split across several SKUs that depend on production runs; threshold alerts help match production to holiday demand.</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Seasoned vs bare stock alerts for Stargazer</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>Hi Peter,
 I noticed Stargazer makes its skillets in Allentown and offers both the 10.5-inch and 12-inch in seasoned or bare finishes. That means every size is really two separate stock items, each tied to your own production runs.
@@ -11685,133 +11536,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>https://stargazercastiron.com/collections/cookware</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>https://stargazercastiron.com/pages/contact</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr">
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr">
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE78" t="n">
+      <c r="AE77" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>US-078</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>US-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>That Detail Shop</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>https://thatdetailshop.com</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Auto detailing products and supplies</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Automotive accessories</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
         <is>
           <t>info@thatdetailshop.com</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>https://shop.app/m/thatdetailshop/collections/490793074966/detailing-products</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Blackline Crystal Glass Cleaner (16 oz single, 16 oz bundle, Ultimate Bundle); Owners Pride Ceramic Detailer (16 oz and gallon); Spit Shine Carnauba Spray Wax</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>That Detail Shop in Evans, GA sells detailing products in size and bundle options, like the Blackline Crystal Glass Cleaner in a 16 oz bottle, 16 oz bundle or Ultimate Bundle, and offers local pickup at Thatdtailguy Auto Detailing.</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>Bundle-aware inventory so bundle variants deduct component stock, plus back-in-stock notifications for out-of-stock sizes and auto-routing of local pickup orders.</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>Several listed sizes/bundles showed as out of stock; bundles share component stock and local pickup orders need separate handling.</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Bundle stock idea for That Detail Shop</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>Hi That Detail Shop team,
 I noticed the Blackline Crystal Glass Cleaner comes as a single 16 oz bottle, a 16 oz bundle and an Ultimate Bundle, and you also offer local pickup in Evans. When bundles share the same bottles, stock counts can drift as the holiday rush starts.
@@ -11822,133 +11673,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>https://www.thatdetailshop.com/products/blackline%C2%AE-crystal-glass-cleaner</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>https://www.thatdetailshop.com/policies/shipping-policy</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr">
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr">
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE79" t="n">
+      <c r="AE78" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>US-079</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>US-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>The RX Tea Shop</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>https://therxteashop.com</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Herbal and leaf teas</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
         <is>
           <t>support@therxteashop.com</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>https://shop.app/m/therxteashop</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Soursop Leaf Tea (leaves sourced from a family-operated organic farm in Mexico)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Products are crafted and packaged in Dallas, TX, and the Soursop Leaf Tea is sourced from a family-operated organic farm in Mexico.</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>Low-stock supplier alerts: when soursop leaf stock falls below a reorder point, automatically draft a reorder notice to the farm supplier and pause or set expectations on the product page.</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>A single-origin ingredient from one international supplier means lead times matter, so earlier reorder signals help keep the listing available.</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Soursop leaf reorder alerts</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>Hi The RX Tea Shop team,
 I noticed your Soursop Leaf Tea comes from a family-operated organic farm in Mexico, then gets packaged in Dallas. When an ingredient comes from a single farm across the border, the time between reorder and restock can stretch, and the holiday season usually makes that window tighter.
@@ -11959,145 +11810,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>https://www.therxteashop.com/products/soursop-leaves</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>https://www.therxteashop.com/pages/contact</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr">
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr">
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE80" t="n">
+      <c r="AE79" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>US-080</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>US-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>The Tea Spot</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>https://theteaspot.com</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Loose leaf wellness teas, gift sets, tea subscription</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Maria Uspenski</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Founder &amp; CEO</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>info@theteaspot.com</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>https://shop.app/m/theteaspot</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Good Night, Sleep Tight: Sip Well Gift Set (16-oz mug + 3 sleepy teas) and the monthly Tea Sipping Club</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>The Good Night, Sleep Tight gift set bundles a 16-oz insulated mug with three herbal sleepy teas of 15 pyramid bags each, alongside a $19.95/month Tea Sipping Club.</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Bundle-component inventory sync: deduct mug and individual tea pouch stock when the gift set sells, and reserve stock ahead of monthly club shipments.</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>Gift sets share components with single-tea listings and the subscription draws on the same stock, so holiday gifting can tighten component availability.</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Sleep tea gift set stock idea</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>Hi Maria,
 I came across the Good Night, Sleep Tight gift set on The Tea Spot, pairing the insulated mug with three sleepy teas, and noticed you also run the monthly Tea Sipping Club. With holiday gifting coming up, sets like that tend to pull on the same pouches and mugs sold individually.
@@ -12108,145 +11959,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>https://www.theteaspot.com/products/good-night-sleep-tea-set</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>https://www.theteaspot.com/pages/find-us-in-stores</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr">
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr">
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE81" t="n">
+      <c r="AE80" t="n">
         <v>86</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>US-081</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>US-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>Tubbs Coffee Roasters</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>https://tubbscoffeeroasters.com</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Small batch coffee roaster</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>beans@tubbscoffeeroasters.com</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>https://www.tubbscoffeeroasters.com/policies/refund-policy</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Blends such as Double Eagle (dark-ish with a touch of robusta) and MEGA Blend (50/50 arabica/robusta), 12 oz bags</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Tubbs sells blends like Double Eagle, a dark-ish roast with a touch of robusta, and the 50/50 MEGA Blend in 12 oz bags.</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Track component green-coffee usage per blend (e.g. robusta shared by Double Eagle and MEGA) and trigger reorder notifications to suppliers when component stock drops below a threshold.</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>Blends that share components draw from the same green stock; automated component tracking ties Shopify sales to raw-material reorder points.</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Blend stock idea for Tubbs</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>Hi Jason,
 I noticed Tubbs offers blends like Double Eagle, a dark-ish roast with a touch of robusta, and the 50/50 arabica and robusta MEGA Blend. Since both draw on robusta, sales of one affect what is available for the other, which matters more as holiday orders start coming in.
@@ -12257,145 +12108,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>https://www.tubbscoffeeroasters.com/products/mega-fifty-fifty-blend</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>https://www.tubbscoffeeroasters.com/policies/refund-policy</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr">
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr">
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE82" t="n">
+      <c r="AE81" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>US-082</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>US-081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>Wash Naturals</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>https://washnaturals.com</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Natural body scrubs, gift sets (self-care)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Skincare and beauty products</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Marisa</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Marisa</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>hello@washnaturals.com</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>https://shop.app/m/78b6qxpmh3</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Body scrubs in 2 oz and 8 oz sizes (Vanilla, Eucalipto, Lemon), Prisma Gift Set of nine minis, Limited Edition Scrubs</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Scrubs like Eucalipto and Lemon come in 2 oz and 8 oz, and the Prisma Gift Set bundles nine mini scrubs, alongside a Limited Edition Scrubs collection; one gift set showed as sold out.</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Gift-set component sync with mini-size stock, and back-in-stock/waitlist notifications for sold-out gift sets and limited editions.</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Nine-mini gift sets consume the same 2 oz stock sold individually; a sold-out set indicates demand that a restock alert can capture.</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Prisma set and mini stock</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>Hi Marisa,
 I saw the Prisma Gift Set at Wash Naturals, nine mini scrubs in one box, and that one of your gift sets was showing as sold out. Since the minis are also sold on their own in 2 oz, a busy holiday stretch can drain them faster than expected.
@@ -12406,133 +12257,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>https://washnaturals.com/products/affirmation-gift-set</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>https://washnaturals.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr">
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr">
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE83" t="n">
+      <c r="AE82" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>US-083</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>US-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Wolf Tooth Components</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>https://wolftoothcomponents.com</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Bicycle components and tools</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
         <is>
           <t>sales@wolftoothcomponents.com</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>https://www.wolftoothcomponents.com/collections/components/products/remote-pro</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>ReMote Pro dropper lever (Components collection); ReMote and ReMote Light Action in Limited Edition Olive</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Wolf Tooth released its ReMote and ReMote Light Action levers in a Limited Edition Olive colour, alongside the ReMote Pro in its Components collection, and serves both direct customers and a stocking dealer network.</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Automatically route limited-edition stock between direct-to-consumer and dealer channels, with low-stock alerts and an auto-hide or back-in-stock flow once a limited colour sells through.</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>Limited-edition colourways have finite stock and the brand sells both direct and through dealers (dealers@ inbox, dealer pages), so channel-aware inventory rules fit.</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Limited Olive stock idea</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>Hi Wolf Tooth team,
 I saw the Limited Edition Olive release of the ReMote and ReMote Light Action levers, and that you also supply a network of stocking dealers. Limited colours with a fixed quantity can be tricky to split between direct orders and dealer orders, particularly heading into the holidays.
@@ -12543,145 +12394,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>https://www.wolftoothcomponents.com/blogs/news/wolf-tooth-remote-and-remote-light-action-in-limited-edition-olive</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>https://www.wolftoothcomponents.com/pages/support</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr">
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr">
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE84" t="n">
+      <c r="AE83" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>US-084</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>US-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>Year of Ours</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>https://yearofours.com</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Women's activewear and swimwear made in Los Angeles</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Eleanor Haycock</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Eleanor</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Co-founder</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>team@yearofours.com</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>https://yearofours.com/collections/leggings</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Leggings (41 styles) and Sports Bras (38 styles) collections, sizes XS-2X</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Year of Ours offers around 40 leggings and 38 sports bra styles in XS-2X across many colours, produced in Los Angeles.</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Weekly fastest-selling variant report with automatic reorder notes to the LA production partner.</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>A wide size/colour matrix across ~80 core styles benefits from automated velocity tracking ahead of holiday demand.</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Leggings variant report for Year of Ours</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>Hi Eleanor,
 I was looking through the Year of Ours leggings and sports bra collections, around 40 styles each in sizes XS to 2X and colours like cobalt, cherry/white and steel grey, all produced in Los Angeles. That is a lot of size and colour combinations to keep balanced as holiday demand builds.
@@ -12692,145 +12543,145 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>https://yearofours.com/collections/leggings</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>https://yearofours.com/pages/contact-us</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr">
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr">
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE85" t="n">
+      <c r="AE84" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>US-085</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>US-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>Zoë Chicco</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>https://zoechicco.com</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Handmade 14k gold fine jewelry, initial and charm pieces</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Jewelry and accessories</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Zoë Chicco</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Zoë</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>direct@zoechicco.com</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>https://zoechicco.com/products/14k-gold-initial-ring</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>14k Gold Initial Letter Ring (made to order, yellow/rose/white gold) and 2 Initial Letter Ring in half sizes 4-9</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>The 14k Gold Initial Letter Ring is made to order in yellow, rose or white gold, and the two-initial version comes in half sizes 4 to 9, handmade in the Los Angeles studio.</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>Generate made-to-order production tickets with letter(s), gold colour and size, and send customers automatic status updates as each piece moves through production.</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>Each initial ring combines letter choice, gold colour and half size and is made to order, so every order carries unique production data.</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Initial ring orders before the holidays</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>Hi Zoë,
 I was looking at your 14k Gold Initial Letter Ring, made to order in yellow, rose or white gold, and the two-initial version in half sizes from 4 to 9. Every one of those orders carries its own letters, colour and size, which adds up quickly in the holiday season.
@@ -12841,60 +12692,60 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>https://zoechicco.com/products/14k-gold-two-initial-ring</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>https://zoechicco.com/pages/contact</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr">
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr">
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE86" t="n">
+      <c r="AE85" t="n">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE86"/>
+  <autoFilter ref="A1:AE85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12905,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13121,7 +12972,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Baby wrap carriers and baby clothing</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -13274,7 +13125,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Organic cotton baby and kids clothing</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -13427,7 +13278,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baby stay-on mitts, boots, gowns and loungewear</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13580,7 +13431,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baby swaddles, bibs, feeding and bath products</t>
+          <t>Baby and children's products</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13733,7 +13584,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Handcrafted herbal body care and skincare</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13886,7 +13737,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Clean skincare and body care</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -14027,7 +13878,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Korean skincare online store</t>
+          <t>Skincare and beauty products</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -14134,7 +13985,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charging cables, chargers, phone cases</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -14265,7 +14116,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Apple Watch bands, licensed collegiate phone cases</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -14396,7 +14247,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leather tech and travel accessories (cord organizers, tablet cases)</t>
+          <t>Electronics and accessories</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14508,73 +14359,226 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Lezat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://lezat.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jaleh Factor</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Jaleh</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>hi@lezat.com</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/lezat</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Activewear collection; Nova Organic Cotton Sport Dress (XS-XL, Black/Ivory)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Lezat makes its organic cotton activewear in-house in Los Angeles; styles like the Nova Organic Cotton Sport Dress run across multiple sizes and colours.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Variant-level low-stock alerts that automatically create production requests for the in-house LA sewing team.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>In-house production plus many size/colour variants means online stock and cutting schedules must stay aligned; automated variant thresholds tie sales to production.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Made-in-LA restock idea for Lezat</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Hi Jaleh,
+I was looking at the Lezat activewear collection and noticed how many styles, like the Nova Organic Cotton Sport Dress, run across several sizes and colours while being sewn in-house in Los Angeles. With holiday orders coming, keeping in-house production and online stock in step can get busy.
+I build Shopify automation systems that help stores simplify inventory updates, order processing and supplier notifications. One idea for Lezat: when a size or colour variant drops below a set level, Shopify automatically creates a cut-and-sew request for your LA team with recent sales attached.
+Would a variant-level production alert like that be useful for your team?
+Best regards,
+Oseni Ibrahim
+Shopify Automation &amp; Integration Specialist</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://www.lezat.com/collections/activewear</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>https://www.lezat.com/pages/orders-shipping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Email page not pinned (seen on shipping/accessibility snippets); confirm contact_source_url.</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REV-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Noelani The Label</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://noelanithelabel.com</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Handmade-to-order swimwear (Florida)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fashion and clothing brands</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>noelanithelabel@gmail.com</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>https://shop.app/m/a58hpz3fbk</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Seashells Bikini Top &amp; Bottom (sold separately); Tati Top - Ruby</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Noelani The Label's swimwear is handmade to order in a small Florida studio, with tops and bottoms like the Seashells bikini sold separately.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Auto-generated daily sewing list grouped by print and size, plus automatic 'in production' customer updates.</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Made-to-order separates need each order queued and matched correctly; an automated production list and status emails reduce manual tracking.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Made-to-order sewing list for Noelani</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Hi Noelani The Label team,
 I saw that your swimwear, including the Seashells bikini top and bottom and the Tati Top in Ruby, is handmade to order in your Florida studio. Selling tops and bottoms separately is great for fit, but it also means every made-to-order piece needs to be queued correctly.
@@ -14585,149 +14589,149 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://noelanithelabel.com/products/seashells-bikini-top</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>https://noelanithelabel.com/products/tati-top-ruby</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>NEEDS_REVIEW</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>email domain not the business; Email is the brand's own Gmail shown on product pages (sizing questions); Florida studio stated on About Us page; owner not named.</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE13" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REV-012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REV-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Hoes For Clothes</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://hoesforclothes.com</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Handmade bikinis and hand-printed tees (Southern California)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Baby and children's products</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Sasha Tarnovsky</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Sasha</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Co-owner (partnership with Andrew Burror)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>hoesforclothes.info@gmail.com</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>https://shop.app/m/hoesforclothes/collections/shop_all</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Raykini top (XS-2XL); Manta Ray Spandex thong (5 colours, XS-2XL); custom baby tees</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Hoes For Clothes sells handmade bikinis and tees hand printed or embroidered in a small Southern California studio, and its pages note handmade takes time.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Auto-tag and route custom-tee and handmade-bikini orders into separate queues with automated estimated ship-date emails.</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Mixed handmade, custom and printed items have different lead times; automated routing and timeline emails build on the store's existing 'handmade takes time' messaging.</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Custom order queues for Hoes For Clothes</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Hi Sasha,
 I was browsing Hoes For Clothes and noticed the handmade bikinis, like the Raykini top in XS to 2XL and the Manta Ray thong in five colours, alongside custom baby tees made in your Southern California studio. Your pages already say handmade takes time, which makes clear order timelines even more valuable as the holidays get closer.
@@ -14738,121 +14742,14 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>https://hoesforclothes.com/products/raykini</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>https://hoesforclothes.com/pages/contact-us</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>PUBLICLY_LISTED</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NEEDS_REVIEW</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>NOT_SENT</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>NO_REPLY</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>email domain not the business; Owners named on About Us page; contact address is a brand Gmail inbox.</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REV-013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Wolaco</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://wolaco.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Activewear (New York)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>info@wolaco.com</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>General inbox</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://www.wolaco.com/pages/contact</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>https://www.wolaco.com/pages/contact</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -14889,7 +14786,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; No specific product/collection detail verified (search budget exhausted); Shopify evidence only /pages/ URL; NY location from search summary.</t>
+          <t>email domain not the business; Owners named on About Us page; contact address is a brand Gmail inbox.</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -14898,7 +14795,7 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -14909,12 +14806,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zuco Swim</t>
+          <t>Wolaco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://zucoswim.com</t>
+          <t>https://wolaco.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14924,7 +14821,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sustainable handmade swimwear</t>
+          <t>Fashion and clothing brands</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -14932,7 +14829,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>zucoswim@gmail.com</t>
+          <t>info@wolaco.com</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -14947,39 +14844,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://shop.app/m/zucoswimwear</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>'Zukinis' - hand sewn, made-to-order swimwear</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Zuco Swim's Zukinis are hand sewn and made to order.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Made-to-order production queue and automated order-status emails.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Made-to-order handmade swimwear needs orders queued and customers updated.</t>
-        </is>
-      </c>
+          <t>https://www.wolaco.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://zucoswim.com/</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://zucoswim.com/pages/contact</t>
+          <t>https://www.wolaco.com/pages/contact</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -15016,7 +14893,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>email domain not the business; missing personalized_subject; missing personalized_email_body; US location not explicitly stated (only 'delivery within 3-5 business days in USA'); no email drafted.</t>
+          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; No specific product/collection detail verified (search budget exhausted); Shopify evidence only /pages/ URL; NY location from search summary.</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -15025,7 +14902,7 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -15036,12 +14913,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bear KompleX</t>
+          <t>Zuco Swim</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://bearkomplex.com</t>
+          <t>https://zucoswim.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15051,7 +14928,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fitness accessories</t>
+          <t>Fashion and clothing brands</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -15059,7 +14936,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GetBetter@BearKompleX.com</t>
+          <t>zucoswim@gmail.com</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -15074,19 +14951,39 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://bearkomplex.com/pages/contact-bear-komplex</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+          <t>https://shop.app/m/zucoswimwear</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>'Zukinis' - hand sewn, made-to-order swimwear</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Zuco Swim's Zukinis are hand sewn and made to order.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Made-to-order production queue and automated order-status emails.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Made-to-order handmade swimwear needs orders queued and customers updated.</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://zucoswim.com/</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://bearkomplex.com/pages/contact-bear-komplex</t>
+          <t>https://zucoswim.com/pages/contact</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -15123,7 +15020,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; Shopify URL structure, US location (Crown Point, Indiana) and email verified; no specific product/collection detail verified (search budget exhausted). Email not written.</t>
+          <t>email domain not the business; missing personalized_subject; missing personalized_email_body; US location not explicitly stated (only 'delivery within 3-5 business days in USA'); no email drafted.</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -15132,7 +15029,7 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -15143,12 +15040,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Element 26</t>
+          <t>Bear KompleX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://element26.co</t>
+          <t>https://bearkomplex.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15158,7 +15055,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fitness accessories</t>
+          <t>Fitness and sports equipment</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -15166,7 +15063,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Support@element26.co</t>
+          <t>GetBetter@BearKompleX.com</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -15181,7 +15078,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://element26.co/policies/privacy-policy</t>
+          <t>https://bearkomplex.com/pages/contact-bear-komplex</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -15193,7 +15090,7 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://element26.co/policies/privacy-policy</t>
+          <t>https://bearkomplex.com/pages/contact-bear-komplex</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -15230,7 +15127,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; Shopify URL structure, US location (Austin, Texas) and email verified; no specific product/collection detail verified (search budget exhausted). Email not written.</t>
+          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; Shopify URL structure, US location (Crown Point, Indiana) and email verified; no specific product/collection detail verified (search budget exhausted). Email not written.</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -15250,85 +15147,192 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Element 26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://element26.co</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Support@element26.co</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://element26.co/policies/privacy-policy</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://element26.co/policies/privacy-policy</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PUBLICLY_LISTED</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; Shopify URL structure, US location (Austin, Texas) and email verified; no specific product/collection detail verified (search budget exhausted). Email not written.</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REV-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Alaska Rug Company</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://alaskarugcompany.com</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Handwoven rope rugs from new and recycled Alaska fishing rope, plus coastal home decor</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fitness and sports equipment</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Jen Luton</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Jen</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Co-owner (with Ryan Burnard, since July 2023)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>alaskarugcompany@gmail.com</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>https://shop.app/m/m8htucf9ne</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Made in AK rope rugs collection - sizes from 20" x 20" to 72" x 24" runners in two-tone colorways (e.g. Natural &amp; Silver, White &amp; Black)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Each rope rug is hand-knotted in Alaska from marine-grade or salvaged fishing rope, listed in many sizes and two-colour combinations, and many pieces are one-of-a-kind.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Automatically unpublish or mark sold one-of-a-kind rugs the moment they sell, and send a weaving-queue notification for repeatable size/colour rugs when stock reaches zero.</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>A mix of unique hand-knotted pieces and repeatable size/colour listings benefits from rules that treat single-quantity items differently from re-weavable ones.</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Rope rug stock rules for Alaska Rug Co.</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Hi Jen,
 I enjoyed reading how your rope rugs are hand-knotted from new and salvaged Alaska fishing rope, with sizes running from 20 x 20 accents up to 72-inch runners in two-tone colorways. With holiday gifting ahead, keeping those listings accurate matters.
@@ -15339,123 +15343,16 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>https://alaskarugcompany.com/collections/rugs/made-in-ak</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>https://alaskarugcompany.com/pages/faqs</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>PUBLICLY_LISTED</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NEEDS_REVIEW</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>NOT_SENT</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>NO_REPLY</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>email domain not the business</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REV-018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Copano Candle Company</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://copanocandleco.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Women-owned hand-poured coconut-soy candles inspired by the Texas coast (Rockport, TX)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>General inbox</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://shop.app/m/copanocandlecompany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Collections incl. The Kraken, Oma's Haus, Retail - All</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>https://copanocandleco.com/collections/the-kraken</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
@@ -15490,7 +15387,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>no valid email; no contact source URL; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; No public email found in search results (contact page exists but address not shown); email not written.</t>
+          <t>email domain not the business</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -15499,7 +15396,7 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -15510,12 +15407,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fewer Finer</t>
+          <t>Copano Candle Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://fewerfiner.com</t>
+          <t>https://copanocandleco.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15525,7 +15422,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Personalizable fine jewelry with engraving</t>
+          <t>Home decor and furniture</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -15544,44 +15441,28 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://fewerfiner.com/collections/engravable-fine-jewelry</t>
+          <t>https://shop.app/m/copanocandlecompany</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Engravable Fine Jewelry collection; Customizable Fine Jewelry (hand engraving, laser engraving, birthstone and diamond additions)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Brooklyn-based Fewer Finer offers personalizable pieces with hand engraving, laser engraving or birthstone and diamond additions.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Route engraving/add-on orders automatically to the right engraving workflow with the customization details attached.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Multiple personalization methods per piece mean each order needs routing to a specific production step.</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Engraving orders at Fewer Finer</t>
-        </is>
-      </c>
+          <t>Collections incl. The Kraken, Oma's Haus, Retail - All</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://fewerfiner.com/collections/personalized-customizable-gifts</t>
+          <t>https://copanocandleco.com/collections/the-kraken</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>PUBLICLY_LISTED</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -15613,7 +15494,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>no valid email; no contact source URL; missing personalized_email_body; No public email found in search results (contact section only lists text number (347) 294-0923); no email drafted.</t>
+          <t>no valid email; no contact source URL; missing personalized_store_observation; missing inventory_order_automation_opportunity; missing personalized_subject; missing personalized_email_body; No public email found in search results (contact page exists but address not shown); email not written.</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -15633,12 +15514,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smithey Ironware</t>
+          <t>Fewer Finer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://smithey.com</t>
+          <t>https://fewerfiner.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15648,58 +15529,181 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cast iron and carbon steel cookware</t>
+          <t>Jewelry and accessories</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://fewerfiner.com/collections/engravable-fine-jewelry</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Engravable Fine Jewelry collection; Customizable Fine Jewelry (hand engraving, laser engraving, birthstone and diamond additions)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Brooklyn-based Fewer Finer offers personalizable pieces with hand engraving, laser engraving or birthstone and diamond additions.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Route engraving/add-on orders automatically to the right engraving workflow with the customization details attached.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Multiple personalization methods per piece mean each order needs routing to a specific production step.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Engraving orders at Fewer Finer</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>https://fewerfiner.com/collections/personalized-customizable-gifts</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>no valid email; no contact source URL; missing personalized_email_body; No public email found in search results (contact section only lists text number (347) 294-0923); no email drafted.</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REV-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Smithey Ironware</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://smithey.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kitchen and household products</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>support@smithey.com</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>https://smithey.com/policies/terms-of-service</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>The Founder's 3-Piece Set (No. 8 Chef Skillet, No. 10, No. 12 Cast Iron Skillets); Set of 4 No. 6 Skillets</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Smithey offers The Founder's 3-Piece Set with the No. 8 Chef, No. 10 and No. 12 skillets, as well as a Set of 4 No. 6 Skillets.</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Component-based availability for multi-skillet sets and corporate gifting order routing.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sets reuse individual skillet SKUs and a separate corporate gifting channel exists (gifting@smithey.com).</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Skillet set stock idea for Smithey</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Hi Smithey team,
 I saw The Founder's 3-Piece Set pairs the No. 8 Chef, No. 10 and No. 12 skillets, and there's also a Set of 4 No. 6 Skillets alongside your corporate gifting program.
@@ -15710,121 +15714,121 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://smithey.com/products/the-founders-3-piece-set</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://smithey.com/a/faq/</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>NEEDS_REVIEW</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>US location not stated in search snippets (only an 843 phone number); likely mid-size/well-known brand; no decision maker verified.</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE22" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REV-021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REV-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Marquette Castings</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://marquettecastings.com</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Cast iron cookware</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kitchen and household products</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>support@marquettecastings.com</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>https://www.marquettecastings.com/pages/contact</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Quick inventory idea for Marquette Castings</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Hi Marquette Castings team,
 I came across Marquette Castings while looking at independent cast iron makers, and your contact page made it easy to find the right inbox. As an independent cast iron maker, you likely see demand shift between sizes during gifting season.
@@ -15835,133 +15839,133 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://www.marquettecastings.com/pages/contact</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>NEEDS_REVIEW</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>no research source URL; missing product_or_collection; missing personalized_store_observation; missing inventory_order_automation_opportunity; No verified product/collection detail and no US location statement in results (810 phone number only); email draft is generic and must be personalised before use.</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE23" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REV-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REV-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>WanderDog Designs</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://wanderdogdesigns.com</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Handmade yacht rope dog leashes and collars</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pet products and accessories</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>wanderdogdesigns@gmail.com</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>https://shop.app/m/5r0y4zdh18</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Rope Slip Lead; 'Small but Mighty' custom dog leashes collection; lifetime guarantee on rope leashes/collars</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Every leash and collar is handmade from yacht rope with a lifetime guarantee, and the Small but Mighty collection offers custom leashes.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Custom-order workflow: capture rope colour/length choices into a production queue and send automatic status updates.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Custom handmade items need order details passed cleanly to production.</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Custom leash order flow idea</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Hi WanderDog Designs team,
 I noticed every leash and collar you make is handmade from yacht rope and backed by a lifetime guarantee, and the Small but Mighty collection offers custom leashes. Custom orders like these usually carry several details that need to reach the workbench correctly, especially as holiday orders start arriving.
@@ -15972,137 +15976,137 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>https://wanderdogdesigns.com/collections/small-but-mighty</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://wanderdogdesigns.com/policies/refund-policy</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>PUBLICLY_LISTED</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>NEEDS_REVIEW</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>NOT_SENT</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>NO_REPLY</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>email domain not the business; US location not verified in search results; email is a Gmail address (listed on own policy pages).</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE24" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REV-023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REV-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Clinical Traditions Herb Co.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://clinicaltraditions.com</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Herbal tinctures and elixirs</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Health and wellness products</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>ClinicalTraditions@gmail.com</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>General inbox</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>https://shop.app/m/348vnqfwpx</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Tinctures in 1, 2 and 4 oz (Lion Heart Elixir, Move Easy Elixir, Nourishing Bitters)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Elixirs such as Lion Heart and Nourishing Bitters come in 1, 2 and 4 oz bottles, with herbs grown in Jacksonville, FL by women farmers.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Size-variant stock tracking that converts bulk tincture batches into bottle-level availability and alerts before a size runs out.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Three sizes per tincture drawn from the same farm-grown batch makes batch-to-variant inventory updates a natural automation.</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Tincture size stock idea</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Hi Clinical Traditions team,
 I noticed your elixirs, like Lion Heart and Nourishing Bitters, come in 1, 2 and 4 oz bottles, with herbs grown right there in Jacksonville. When one farm batch is split across three bottle sizes, keeping each size's count accurate can take a lot of manual updating, especially around the holidays.
@@ -16113,153 +16117,14 @@
 Shopify Automation &amp; Integration Specialist</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>https://www.clinicaltraditions.com/products/lion-heart-elixir-a-stress-reducing-tincture</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>https://www.clinicaltraditions.com/pages/contact</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>PUBLICLY_LISTED</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NEEDS_REVIEW</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>NOT_SENT</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>NO_REPLY</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>email domain not the business; Email is a Gmail address but publicly listed on the store's own contact page. Jacksonville, FL per shop.app listing and product page. No decision maker verified.</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REV-024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Grassroots Herb Supply</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://grassrootsherbsupply.com</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Loose leaf tea blends and bulk herbs</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sterling Mitchell</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Sterling</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Co-owner (with Jenn Mitchell)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ster@grassrootsherbsupply.com</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Decision-maker</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://shop.app/m/grassrootsherbsupply</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Dreamwalker tea blend and California Poppy bulk herb in 1 oz, 4 oz, 8 oz and 1 lb</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tea blends and bulk herbs, such as the Dreamwalker blend, are sold in four sizes from 1 oz to 1 lb.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Weight-based inventory: track herbs by total weight and update all four size variants automatically.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Four weight variants share one bulk supply, so weight-based tracking keeps every size accurate.</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>https://grassrootsherbsupply.com/products/california-poppy-cs</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>https://grassrootsherbsupply.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -16296,7 +16161,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>missing personalized_subject; missing personalized_email_body; US location not verified in search results (search budget exhausted). Email/owners/product verified; email not written.</t>
+          <t>email domain not the business; Email is a Gmail address but publicly listed on the store's own contact page. Jacksonville, FL per shop.app listing and product page. No decision maker verified.</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -16305,7 +16170,7 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
@@ -16316,12 +16181,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Golden Cloud Brand</t>
+          <t>Grassroots Herb Supply</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://goldencloudbrand.com</t>
+          <t>https://grassrootsherbsupply.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16331,32 +16196,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mushroom teas</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Abbe Turner</t>
+          <t>Sterling Mitchell</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Abbe</t>
+          <t>Sterling</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-owner (with Jenn Mitchell)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>info@goldencloudbrand.com</t>
+          <t>ster@grassrootsherbsupply.com</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>General inbox</t>
+          <t>Decision-maker</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -16366,39 +16231,39 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://shop.app/m/ke9wg18qpt</t>
+          <t>https://shop.app/m/grassrootsherbsupply</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Golden Cloud Variety Pack; Relax Mushroom Tea</t>
+          <t>Dreamwalker tea blend and California Poppy bulk herb in 1 oz, 4 oz, 8 oz and 1 lb</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sells a Golden Cloud Variety Pack of its mushroom teas.</t>
+          <t>Tea blends and bulk herbs, such as the Dreamwalker blend, are sold in four sizes from 1 oz to 1 lb.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Variety-pack component sync with single-flavor stock.</t>
+          <t>Weight-based inventory: track herbs by total weight and update all four size variants automatically.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Variety packs share stock with single teas.</t>
+          <t>Four weight variants share one bulk supply, so weight-based tracking keeps every size accurate.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.goldencloudbrand.com/</t>
+          <t>https://grassrootsherbsupply.com/products/california-poppy-cs</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.goldencloudbrand.com/pages/contact-us</t>
+          <t>https://grassrootsherbsupply.com/pages/contact-us</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -16435,7 +16300,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>missing personalized_subject; missing personalized_email_body; US location not verified; Abbe Turner signs contact page (founder per snippet). Email not written.</t>
+          <t>missing personalized_subject; missing personalized_email_body; US location not verified in search results (search budget exhausted). Email/owners/product verified; email not written.</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -16444,7 +16309,7 @@
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
@@ -16455,12 +16320,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kimball Botanicals</t>
+          <t>Golden Cloud Brand</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://kimballbotanicals.com</t>
+          <t>https://goldencloudbrand.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16470,17 +16335,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Organic herbal supplements, bath and body</t>
+          <t>Specialty food and beverage brands</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Isaiah Kimball</t>
+          <t>Abbe Turner</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Abbe</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -16488,8 +16353,16 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>info@goldencloudbrand.com</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>General inbox</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>YES</t>
@@ -16497,40 +16370,44 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://shop.app/m/kimballbotanicals/collections/490985029946/herbal-bath-and-body</t>
+          <t>https://shop.app/m/ke9wg18qpt</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>USDA Organic Oil of Oregano Capsules 900mg (made fresh to order); Herbal Bath and Body collection</t>
+          <t>Golden Cloud Variety Pack; Relax Mushroom Tea</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Products are made fresh to order by the family in a South Carolina cGMP facility.</t>
+          <t>Sells a Golden Cloud Variety Pack of its mushroom teas.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Made-to-order production queue generated from incoming Shopify orders.</t>
+          <t>Variety-pack component sync with single-flavor stock.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Made-fresh-to-order model benefits from automated production lists.</t>
+          <t>Variety packs share stock with single teas.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://kimballbotanicals.com/products/usda-organic-oil-of-oregano-capsules-900mg-vegetarian-capsules-made-fresh-to-order-with-zero-fillers</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>https://www.goldencloudbrand.com/</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.goldencloudbrand.com/pages/contact-us</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>PUBLICLY_LISTED</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -16562,7 +16439,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>no valid email; no contact source URL; missing personalized_subject; missing personalized_email_body; No public email found in search results.</t>
+          <t>missing personalized_subject; missing personalized_email_body; US location not verified; Abbe Turner signs contact page (founder per snippet). Email not written.</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -16571,7 +16448,7 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
@@ -16582,12 +16459,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Full Flower Herbs</t>
+          <t>Kimball Botanicals</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://fullflowerherbs.com</t>
+          <t>https://kimballbotanicals.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16597,17 +16474,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Herbal tinctures and teas</t>
+          <t>Health and wellness products</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lindsay Perry</t>
+          <t>Isaiah Kimball</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lindsay</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -16624,34 +16501,34 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://shop.app/m/pchvfae9u1</t>
+          <t>https://shop.app/m/kimballbotanicals/collections/490985029946/herbal-bath-and-body</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Custom Blend Herbal Tincture in 4/6/8/10 oz; tinctures in 1/2/4 oz with 8 oz refill bottles</t>
+          <t>USDA Organic Oil of Oregano Capsules 900mg (made fresh to order); Herbal Bath and Body collection</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Offers custom-blend tinctures in four sizes and 8 oz refill bottles.</t>
+          <t>Products are made fresh to order by the family in a South Carolina cGMP facility.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Refill reminders and variant stock sync.</t>
+          <t>Made-to-order production queue generated from incoming Shopify orders.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Refill bottles suggest repeat purchases.</t>
+          <t>Made-fresh-to-order model benefits from automated production lists.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.fullflowerherbs.com/products/custom-blend-herbal-tincture</t>
+          <t>https://kimballbotanicals.com/products/usda-organic-oil-of-oregano-capsules-900mg-vegetarian-capsules-made-fresh-to-order-with-zero-fillers</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -16689,7 +16566,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>no valid email; no contact source URL; missing personalized_subject; missing personalized_email_body; No public email found; base location not confirmed (herbs grown in NC Piedmont).</t>
+          <t>no valid email; no contact source URL; missing personalized_subject; missing personalized_email_body; No public email found in search results.</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -16701,8 +16578,135 @@
         <v>40</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>REV-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Full Flower Herbs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://fullflowerherbs.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Specialty food and beverage brands</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lindsay Perry</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lindsay</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://shop.app/m/pchvfae9u1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Custom Blend Herbal Tincture in 4/6/8/10 oz; tinctures in 1/2/4 oz with 8 oz refill bottles</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Offers custom-blend tinctures in four sizes and 8 oz refill bottles.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Refill reminders and variant stock sync.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Refill bottles suggest repeat purchases.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>https://www.fullflowerherbs.com/products/custom-blend-herbal-tincture</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>NOT_SENT</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>NO_REPLY</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>no valid email; no contact source URL; missing personalized_subject; missing personalized_email_body; No public email found; base location not confirmed (herbs grown in NC Piedmont).</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE28"/>
+  <autoFilter ref="A1:AE29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
